--- a/exports/MUTHOOTFIN_full_report.xlsx
+++ b/exports/MUTHOOTFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.55</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>1489.45</v>
+        <v>1466.95</v>
       </c>
       <c r="I2" t="n">
         <v>1478.90875</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.47</v>
+        <v>-4.93</v>
       </c>
       <c r="L2" t="n">
-        <v>4.27</v>
+        <v>5.66</v>
       </c>
       <c r="M2" t="n">
         <v>0.33</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.55208333334</v>
+        <v>44623.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1390</v>
+        <v>1432</v>
       </c>
       <c r="I3" t="n">
         <v>1414.663559112944</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="L3" t="n">
         <v>2.36</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.75</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44644.55208333334</v>
+        <v>44645.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>1348.45</v>
+        <v>1310</v>
       </c>
       <c r="I4" t="n">
         <v>1327.072660031481</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.83</v>
+        <v>-8.52</v>
       </c>
       <c r="L4" t="n">
-        <v>7.33</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>0.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.83</v>
+        <v>3.37</v>
       </c>
       <c r="O4" t="n">
         <v>2.16</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>7.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44655.55208333334</v>
+        <v>44656.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1360</v>
+        <v>1370.6</v>
       </c>
       <c r="I5" t="n">
         <v>1364.670786092278</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.82</v>
+        <v>-4.63</v>
       </c>
       <c r="L5" t="n">
-        <v>4.35</v>
+        <v>4.89</v>
       </c>
       <c r="M5" t="n">
         <v>1.19</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>5.18</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1336.75</v>
+        <v>1297.5</v>
       </c>
       <c r="I6" t="n">
         <v>1318.846209370607</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.47</v>
+        <v>-5.33</v>
       </c>
       <c r="L6" t="n">
-        <v>2.73</v>
+        <v>5.47</v>
       </c>
       <c r="M6" t="n">
         <v>0.93</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.42</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44743.38541666666</v>
+        <v>44743.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1017.6</v>
+        <v>1037</v>
       </c>
       <c r="I7" t="n">
         <v>1025.520174866696</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>74</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>21.57</v>
+        <v>20.08</v>
       </c>
       <c r="L7" t="n">
         <v>3.73</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.89</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44755.55208333334</v>
+        <v>44756.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1003</v>
+        <v>995.75</v>
       </c>
       <c r="I8" t="n">
         <v>999.9205586929643</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.28</v>
+        <v>-3.98</v>
       </c>
       <c r="L8" t="n">
-        <v>3.54</v>
+        <v>4.76</v>
       </c>
       <c r="M8" t="n">
         <v>0.45</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.29</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44760.38541666666</v>
+        <v>44760.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>1039.4</v>
+        <v>1055.45</v>
       </c>
       <c r="I9" t="n">
         <v>1041.332466893258</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.38</v>
+        <v>-6</v>
       </c>
       <c r="L9" t="n">
-        <v>4.64</v>
+        <v>6.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.41</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.79</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44785.55208333334</v>
+        <v>44789.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1188</v>
+        <v>1037.55</v>
       </c>
       <c r="I10" t="n">
         <v>1120.536686451279</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>12.56</v>
+        <v>-1.7</v>
       </c>
       <c r="L10" t="n">
-        <v>4.11</v>
+        <v>4.37</v>
       </c>
       <c r="M10" t="n">
-        <v>0.35</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>12.21</v>
       </c>
       <c r="O10" t="n">
         <v>3.75</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.97</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44831.55208333334</v>
+        <v>44832.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1013</v>
+        <v>1046.5</v>
       </c>
       <c r="I11" t="n">
         <v>1016.331318077129</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K11" t="n">
-        <v>2.37</v>
+        <v>-0.86</v>
       </c>
       <c r="L11" t="n">
         <v>5.34</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1105.95</v>
+        <v>1064.2</v>
       </c>
       <c r="I12" t="n">
         <v>1066.729812688387</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>5.68</v>
+        <v>1.69</v>
       </c>
       <c r="L12" t="n">
         <v>4.65</v>
@@ -1125,7 +1268,7 @@
         <v>1.83</v>
       </c>
       <c r="N12" t="n">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>2.86</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.25</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44896.38541666666</v>
+        <v>44896.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1102.9</v>
+        <v>1110</v>
       </c>
       <c r="I13" t="n">
         <v>1107.172956511202</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.64</v>
+        <v>-4.3</v>
       </c>
       <c r="L13" t="n">
         <v>5.8</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.62</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44907.38541666666</v>
+        <v>44907.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1098.7</v>
+        <v>1094.7</v>
       </c>
       <c r="I14" t="n">
         <v>1097.041859091483</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.02</v>
+        <v>-1.38</v>
       </c>
       <c r="L14" t="n">
         <v>2.52</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45005.55208333334</v>
+        <v>45006.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>950</v>
+        <v>967.3</v>
       </c>
       <c r="I15" t="n">
         <v>953.3449437667833</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>98</v>
+        <v>98.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>13.22</v>
+        <v>11.64</v>
       </c>
       <c r="L15" t="n">
         <v>2.86</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.98</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1052</v>
+        <v>1026.7</v>
       </c>
       <c r="I16" t="n">
         <v>1029.187170185199</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K16" t="n">
-        <v>8.76</v>
+        <v>6.14</v>
       </c>
       <c r="L16" t="n">
         <v>2.92</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.8</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1035</v>
+        <v>1131.5</v>
       </c>
       <c r="I17" t="n">
         <v>1077.317318370003</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-10.21</v>
       </c>
       <c r="L17" t="n">
-        <v>2.95</v>
+        <v>10.45</v>
       </c>
       <c r="M17" t="n">
-        <v>0.37</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>-1.62</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.93</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1350</v>
+        <v>1280.15</v>
       </c>
       <c r="I18" t="n">
         <v>1313.227431837796</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K18" t="n">
-        <v>19.31</v>
+        <v>13.14</v>
       </c>
       <c r="L18" t="n">
         <v>7.56</v>
       </c>
       <c r="M18" t="n">
-        <v>0.91</v>
+        <v>2.19</v>
       </c>
       <c r="N18" t="n">
-        <v>1.78</v>
+        <v>5.44</v>
       </c>
       <c r="O18" t="n">
         <v>8.449999999999999</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.48</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45183.55208333334</v>
+        <v>45184.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1290.5</v>
+        <v>1317.05</v>
       </c>
       <c r="I19" t="n">
         <v>1304.316862565387</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.88</v>
       </c>
       <c r="L19" t="n">
         <v>3.15</v>
@@ -1524,7 +1751,7 @@
         <v>0.73</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="O19" t="n">
         <v>-5.44</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.42</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45191.38541666666</v>
+        <v>45191.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>1275.3</v>
+        <v>1265</v>
       </c>
       <c r="I20" t="n">
         <v>1274.106914526398</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.17</v>
+        <v>-3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>3.55</v>
+        <v>4.04</v>
       </c>
       <c r="M20" t="n">
         <v>0.18</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45216.38541666666</v>
+        <v>45216.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>1245.55</v>
+        <v>1247.75</v>
       </c>
       <c r="I21" t="n">
         <v>1246.120005421098</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>24.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="L21" t="n">
         <v>1.27</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>3.72</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45239.55208333334</v>
+        <v>45240.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1309</v>
+        <v>1260.75</v>
       </c>
       <c r="I22" t="n">
         <v>1276.742906533985</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>4.91</v>
+        <v>1.04</v>
       </c>
       <c r="L22" t="n">
-        <v>0.78</v>
+        <v>2.54</v>
       </c>
       <c r="M22" t="n">
-        <v>0.32</v>
+        <v>5.27</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
         <v>0.59</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.05</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45246.38541666666</v>
+        <v>45246.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1321.6</v>
+        <v>1324.9</v>
       </c>
       <c r="I23" t="n">
         <v>1324.441257015305</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.83</v>
+        <v>-5.09</v>
       </c>
       <c r="L23" t="n">
-        <v>5.18</v>
+        <v>5.89</v>
       </c>
       <c r="M23" t="n">
         <v>1.49</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.92</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45306.55208333334</v>
+        <v>45307.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1450.85</v>
+        <v>1433.6</v>
       </c>
       <c r="I24" t="n">
         <v>1443.211246581024</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>60</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>9.51</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>2.52</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>6.04</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1335.7</v>
+        <v>1394.35</v>
       </c>
       <c r="I25" t="n">
         <v>1341.056940505444</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K25" t="n">
-        <v>6.83</v>
+        <v>2.74</v>
       </c>
       <c r="L25" t="n">
-        <v>1.77</v>
+        <v>6.52</v>
       </c>
       <c r="M25" t="n">
-        <v>1.66</v>
+        <v>4.81</v>
       </c>
       <c r="N25" t="n">
         <v>3.77</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.5</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45369.55208333334</v>
+        <v>45370.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1335</v>
+        <v>1330.35</v>
       </c>
       <c r="I26" t="n">
         <v>1331.604903930846</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.26</v>
+        <v>-4.59</v>
       </c>
       <c r="L26" t="n">
-        <v>4.7</v>
+        <v>5.26</v>
       </c>
       <c r="M26" t="n">
         <v>0.45</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.72</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45372.38541666666</v>
+        <v>45372.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1407.8</v>
+        <v>1428</v>
       </c>
       <c r="I27" t="n">
         <v>1409.95700241497</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.82</v>
+        <v>-7.34</v>
       </c>
       <c r="L27" t="n">
-        <v>6.04</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.18</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>6.73</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1651.6</v>
+        <v>1618.2</v>
       </c>
       <c r="I28" t="n">
         <v>1639.888165259801</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>15.66</v>
+        <v>13.32</v>
       </c>
       <c r="L28" t="n">
         <v>1.66</v>
       </c>
       <c r="M28" t="n">
-        <v>2.22</v>
+        <v>4.94</v>
       </c>
       <c r="N28" t="n">
-        <v>1.82</v>
+        <v>3.31</v>
       </c>
       <c r="O28" t="n">
         <v>6.95</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.95</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1703.9</v>
+        <v>1717.35</v>
       </c>
       <c r="I29" t="n">
         <v>1714.520829756498</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.3</v>
+        <v>-6.13</v>
       </c>
       <c r="L29" t="n">
         <v>6.4</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>5.98</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1709.15</v>
+        <v>1650.6</v>
       </c>
       <c r="I30" t="n">
         <v>1655.481293128696</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.48</v>
+        <v>-3.89</v>
       </c>
       <c r="L30" t="n">
-        <v>2.99</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>0.23</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>8.57</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1777.8</v>
+        <v>1798.2</v>
       </c>
       <c r="I31" t="n">
         <v>1791.999001380028</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.71</v>
+        <v>-8.94</v>
       </c>
       <c r="L31" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
         <v>5.8</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.32</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1811.45</v>
+        <v>1782.45</v>
       </c>
       <c r="I32" t="n">
         <v>1783.611658093365</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>0.74</v>
+        <v>-0.88</v>
       </c>
       <c r="L32" t="n">
         <v>5.35</v>
@@ -2265,7 +2648,7 @@
         <v>0.34</v>
       </c>
       <c r="N32" t="n">
-        <v>1.89</v>
+        <v>3.85</v>
       </c>
       <c r="O32" t="n">
         <v>1.05</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>6.14</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45504.55208333334</v>
+        <v>45505.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1832</v>
+        <v>1855.8</v>
       </c>
       <c r="I33" t="n">
         <v>1836.308300604638</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.78</v>
+        <v>-4.12</v>
       </c>
       <c r="L33" t="n">
-        <v>3.63</v>
+        <v>5.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="N33" t="n">
         <v>2.21</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.64</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45510.38541666666</v>
+        <v>45510.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1828.35</v>
+        <v>1783.95</v>
       </c>
       <c r="I34" t="n">
         <v>1785.39603807856</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.48</v>
+        <v>-3.87</v>
       </c>
       <c r="L34" t="n">
         <v>10.01</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.41</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45530.55208333334</v>
+        <v>45531.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1931.75</v>
+        <v>1979.55</v>
       </c>
       <c r="I35" t="n">
         <v>1951.732999416657</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.279999999999999</v>
+        <v>-10.96</v>
       </c>
       <c r="L35" t="n">
-        <v>9.25</v>
+        <v>11.35</v>
       </c>
       <c r="M35" t="n">
         <v>2.56</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45566.38541666666</v>
+        <v>45566.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>1960.05</v>
+        <v>1951.95</v>
       </c>
       <c r="I36" t="n">
         <v>1957.726245432777</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.99</v>
+        <v>-1.39</v>
       </c>
       <c r="L36" t="n">
         <v>2.93</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>5.8</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45610.55208333334</v>
+        <v>45614.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1790</v>
+        <v>1912</v>
       </c>
       <c r="I37" t="n">
         <v>1878.843916598441</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>44</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>8.300000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="L37" t="n">
         <v>2.62</v>
       </c>
       <c r="M37" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.92</v>
+        <v>5.61</v>
       </c>
       <c r="O37" t="n">
         <v>-3.95</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45666.38541666666</v>
+        <v>45666.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>2162</v>
+        <v>2137.1</v>
       </c>
       <c r="I38" t="n">
         <v>2140.335705059399</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>13.08</v>
+        <v>11.77</v>
       </c>
       <c r="L38" t="n">
         <v>3.45</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.63</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45687.38541666666</v>
+        <v>45687.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>2205.9</v>
+        <v>2230</v>
       </c>
       <c r="I39" t="n">
         <v>2225.957910048576</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.22</v>
+        <v>-4.35</v>
       </c>
       <c r="L39" t="n">
         <v>4.47</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.43</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2204.95</v>
+        <v>2126.95</v>
       </c>
       <c r="I40" t="n">
         <v>2149.789762800139</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.12</v>
+        <v>-4.62</v>
       </c>
       <c r="L40" t="n">
-        <v>4.44</v>
+        <v>4.82</v>
       </c>
       <c r="M40" t="n">
         <v>0.96</v>
       </c>
       <c r="N40" t="n">
-        <v>3.36</v>
+        <v>3.43</v>
       </c>
       <c r="O40" t="n">
         <v>0.5</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45729.55208333334</v>
+        <v>45733.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2191</v>
+        <v>2282.2</v>
       </c>
       <c r="I41" t="n">
         <v>2247.450925169885</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.01</v>
+        <v>-7.3</v>
       </c>
       <c r="L41" t="n">
-        <v>4.82</v>
+        <v>8.51</v>
       </c>
       <c r="M41" t="n">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="N41" t="n">
-        <v>2.35</v>
+        <v>4.45</v>
       </c>
       <c r="O41" t="n">
         <v>-3.43</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.34</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2343.8</v>
+        <v>2253.85</v>
       </c>
       <c r="I42" t="n">
         <v>2278.38084443531</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K42" t="n">
-        <v>2.7</v>
+        <v>-1.24</v>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>5.79</v>
       </c>
       <c r="M42" t="n">
-        <v>0.13</v>
+        <v>8.27</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="O42" t="n">
         <v>4.45</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>6.74</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45768.55208333334</v>
+        <v>45769.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2206</v>
+        <v>2289.4</v>
       </c>
       <c r="I43" t="n">
         <v>2261.505569755523</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>2.12</v>
+        <v>-1.58</v>
       </c>
       <c r="L43" t="n">
         <v>3.11</v>
       </c>
       <c r="M43" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="N43" t="n">
         <v>4.68</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>2110.1</v>
+        <v>2093.7</v>
       </c>
       <c r="I44" t="n">
         <v>2097.52011215188</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.83</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L44" t="n">
         <v>9.32</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.09</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45783.55208333334</v>
+        <v>45784.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2244</v>
+        <v>2325.1</v>
       </c>
       <c r="I45" t="n">
         <v>2281.871431475104</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.18</v>
+        <v>-11.05</v>
       </c>
       <c r="L45" t="n">
-        <v>7.72</v>
+        <v>11.79</v>
       </c>
       <c r="M45" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>1.96</v>
+        <v>2.71</v>
       </c>
       <c r="O45" t="n">
         <v>-2.75</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2266</v>
+        <v>2093.5</v>
       </c>
       <c r="I46" t="n">
         <v>2172.425081504723</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.54</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>7.75</v>
+        <v>10.11</v>
       </c>
       <c r="M46" t="n">
         <v>4.03</v>
       </c>
       <c r="N46" t="n">
-        <v>3.03</v>
+        <v>6.97</v>
       </c>
       <c r="O46" t="n">
         <v>2.71</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>13.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2064.9</v>
+        <v>2215.3</v>
       </c>
       <c r="I47" t="n">
         <v>2155.916064485614</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>1.37</v>
+        <v>-5.82</v>
       </c>
       <c r="L47" t="n">
         <v>8.67</v>
@@ -3120,7 +3683,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>2.97</v>
+        <v>6.74</v>
       </c>
       <c r="O47" t="n">
         <v>-6.97</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45870.38541666666</v>
+        <v>45870.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>2607.5</v>
+        <v>2582.5</v>
       </c>
       <c r="I48" t="n">
         <v>2585.423993442253</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>17.7</v>
+        <v>16.58</v>
       </c>
       <c r="L48" t="n">
         <v>6.65</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.16</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45882.55208333334</v>
+        <v>45883.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2515.1</v>
+        <v>2766.9</v>
       </c>
       <c r="I49" t="n">
         <v>2643.756992044894</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>2.61</v>
+        <v>-7.14</v>
       </c>
       <c r="L49" t="n">
-        <v>3.66</v>
+        <v>8.42</v>
       </c>
       <c r="M49" t="n">
-        <v>0.73</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O49" t="n">
         <v>-1.37</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>3272</v>
+        <v>3142.8</v>
       </c>
       <c r="I50" t="n">
         <v>3202.737408692645</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>68.1875</v>
+        <v>70</v>
       </c>
       <c r="K50" t="n">
-        <v>18.26</v>
+        <v>13.59</v>
       </c>
       <c r="L50" t="n">
         <v>5.88</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.84</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45971.38541666666</v>
+        <v>45971.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>3284.8</v>
+        <v>3320</v>
       </c>
       <c r="I51" t="n">
         <v>3309.273245719953</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.52</v>
+        <v>-5.64</v>
       </c>
       <c r="L51" t="n">
-        <v>4.89</v>
+        <v>6.12</v>
       </c>
       <c r="M51" t="n">
         <v>0.7</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.92</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46052.38541666666</v>
+        <v>46052.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>3854.8</v>
+        <v>3818</v>
       </c>
       <c r="I52" t="n">
         <v>3853.907923258117</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>80.83333333333333</v>
+        <v>81</v>
       </c>
       <c r="K52" t="n">
-        <v>16.11</v>
+        <v>15</v>
       </c>
       <c r="L52" t="n">
         <v>1.08</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.4</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46063.38541666666</v>
+        <v>46063.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>3866</v>
+        <v>3888</v>
       </c>
       <c r="I53" t="n">
         <v>3868.072016395315</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.26</v>
+        <v>-1.83</v>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="M53" t="n">
         <v>4.34</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.65</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46065.55208333334</v>
+        <v>46066.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>4070</v>
+        <v>3605.7</v>
       </c>
       <c r="I54" t="n">
         <v>3732.683039799761</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>4.68</v>
+        <v>-7.26</v>
       </c>
       <c r="L54" t="n">
-        <v>1.23</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>0.05</v>
+        <v>4.91</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>11.87</v>
       </c>
       <c r="O54" t="n">
         <v>2.8</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>14.53</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46097.55208333334</v>
+        <v>46098.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>3340.8</v>
+        <v>3408.6</v>
       </c>
       <c r="I55" t="n">
         <v>3395.605026991971</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K55" t="n">
-        <v>7.35</v>
+        <v>5.47</v>
       </c>
       <c r="L55" t="n">
         <v>7.33</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.55</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3300</v>
+        <v>3046.6</v>
       </c>
       <c r="I56" t="n">
         <v>3237.752374618012</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.19</v>
+        <v>-10.62</v>
       </c>
       <c r="L56" t="n">
-        <v>4.48</v>
+        <v>10.75</v>
       </c>
       <c r="M56" t="n">
-        <v>1.84</v>
+        <v>3.33</v>
       </c>
       <c r="N56" t="n">
-        <v>3.29</v>
+        <v>5.85</v>
       </c>
       <c r="O56" t="n">
         <v>2.52</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>11.41</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3240</v>
+        <v>3482.6</v>
       </c>
       <c r="I57" t="n">
         <v>3348.418760030629</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.35</v>
+        <v>-14.31</v>
       </c>
       <c r="L57" t="n">
-        <v>9.92</v>
+        <v>14.55</v>
       </c>
       <c r="M57" t="n">
-        <v>2.79</v>
+        <v>3.7</v>
       </c>
       <c r="N57" t="n">
-        <v>5.66</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O57" t="n">
         <v>-5.85</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>3441</v>
+        <v>3369.5</v>
       </c>
       <c r="I58" t="n">
         <v>3411.07032493077</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.19</v>
+        <v>-3.25</v>
       </c>
       <c r="L58" t="n">
         <v>3.52</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.07</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3525</v>
+        <v>3571.2</v>
       </c>
       <c r="I59" t="n">
         <v>3553.088828224238</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.61</v>
+        <v>-5.99</v>
       </c>
       <c r="L59" t="n">
-        <v>4.86</v>
+        <v>6.32</v>
       </c>
       <c r="M59" t="n">
         <v>2.14</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.13</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3532</v>
+        <v>3304.3</v>
       </c>
       <c r="I60" t="n">
         <v>3331.760699802077</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.1</v>
+        <v>-7.47</v>
       </c>
       <c r="L60" t="n">
-        <v>2.07</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>-0</v>
+        <v>0.23</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="O60" t="n">
         <v>0.2</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>11.02</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>3046</v>
+        <v>3189.5</v>
       </c>
       <c r="I61" t="n">
         <v>3084.692548598779</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K61" t="n">
-        <v>7.82</v>
+        <v>3.47</v>
       </c>
       <c r="L61" t="n">
         <v>6.65</v>
       </c>
       <c r="M61" t="n">
-        <v>1.97</v>
+        <v>2.72</v>
       </c>
       <c r="N61" t="n">
         <v>5.11</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.25</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>3030</v>
+        <v>2983.8</v>
       </c>
       <c r="I62" t="n">
         <v>3006.886199967706</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-5</v>
+        <v>-6.45</v>
       </c>
       <c r="L62" t="n">
-        <v>5.37</v>
+        <v>6.93</v>
       </c>
       <c r="M62" t="n">
         <v>1.46</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.31</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>3050</v>
+        <v>3109</v>
       </c>
       <c r="I63" t="n">
         <v>3103.2686206151</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.22</v>
+        <v>-4.2</v>
       </c>
       <c r="L63" t="n">
-        <v>4.03</v>
+        <v>5.41</v>
       </c>
       <c r="M63" t="n">
         <v>2.26</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>6.91</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>3126.1</v>
+        <v>2886</v>
       </c>
       <c r="I64" t="n">
         <v>2969.608925541289</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>0.55</v>
+        <v>-7.17</v>
       </c>
       <c r="L64" t="n">
-        <v>5.92</v>
+        <v>14.09</v>
       </c>
       <c r="M64" t="n">
-        <v>2.01</v>
+        <v>8</v>
       </c>
       <c r="N64" t="n">
-        <v>2.52</v>
+        <v>7.52</v>
       </c>
       <c r="O64" t="n">
         <v>2.95</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.67</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46253.55208333334</v>
+        <v>46254.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>2854.3</v>
+        <v>2976.7</v>
       </c>
       <c r="I65" t="n">
         <v>2971.569090420769</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K65" t="n">
-        <v>1.1</v>
+        <v>-3.14</v>
       </c>
       <c r="L65" t="n">
-        <v>2.67</v>
+        <v>3.87</v>
       </c>
       <c r="M65" t="n">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="N65" t="n">
-        <v>1.75</v>
+        <v>4.12</v>
       </c>
       <c r="O65" t="n">
         <v>-7.52</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>5.91</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>3090.8</v>
+        <v>3007.3</v>
       </c>
       <c r="I66" t="n">
         <v>3064.908024773266</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>3.83</v>
+        <v>1.03</v>
       </c>
       <c r="L66" t="n">
         <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>0.51</v>
+        <v>1.38</v>
       </c>
       <c r="N66" t="n">
         <v>4.21</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>78</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7176,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.9</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7206,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.3</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7236,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7256,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.2</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7266,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.64</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.03</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7296,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.57</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7306,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.6</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7316,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.55</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7326,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.27</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7336,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.01</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7346,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7356,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7366,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.28</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7376,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.34</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7386,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.05</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7396,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.95</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7406,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
